--- a/MAJSushiConfig/ig/FRImagingMedicationAministrationLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRImagingMedicationAministrationLMCDAFHIR.xlsx
@@ -29,7 +29,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/ConceptMap/FRImagingMedicationAministrationLMCDAFHIR</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/ConceptMap/FRImagingMedicationAministrationLMCDAFHIR</t>
   </si>
   <si>
     <t>Version</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -110,7 +110,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicationAdministration</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicationAdministration|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -161,7 +161,7 @@
     <t>FRLMMedicationAdministration.note</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedication</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedication|0.1.0</t>
   </si>
   <si>
     <t>FRLMMedication.identifyingCode[x]</t>
@@ -182,7 +182,7 @@
     <t>SubstanceAdministration.consumable.manufacturedProduct.manufacturedMaterial.lotNumberText</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDosageInstructions</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDosageInstructions|0.1.0</t>
   </si>
   <si>
     <t>FRLMDosageInstructions.renderedDosageInstruction</t>

--- a/MAJSushiConfig/ig/FRImagingMedicationAministrationLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRImagingMedicationAministrationLMCDAFHIR.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
